--- a/out/LSTM-Mamba1_repeat_5_000006.xlsx
+++ b/out/LSTM-Mamba1_repeat_5_000006.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>1.599521431067185</v>
+        <v>15.28973846592426</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.599521431067185</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>2.199521431067184</v>
+        <v>0.1742763026941591</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>2.199521431067184</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>2.199521431067184</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>2.199521431067184</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>2.199521431067184</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>2.199521431067184</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>2.199521431067184</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>1.599521431067185</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.599521431067185</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.599521431067185</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.599521431067185</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.599521431067185</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.599521431067185</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.599521431067185</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.599521431067185</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.599521431067185</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.599521431067185</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.599521431067185</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.599521431067185</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.599521431067185</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.599521431067185</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.599521431067185</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.599521431067185</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.599521431067185</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.599521431067185</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.599521431067185</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.599521431067185</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.599521431067185</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.599521431067185</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.599521431067185</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.599521431067185</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.599521431067185</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.599521431067185</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.599521431067185</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.599521431067185</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.599521431067185</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.599521431067185</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.599521431067185</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.599521431067185</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,14 +35122,14 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.599521431067185</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.599521431067185</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.000283607674783445</v>
+        <v>-5.113152705365792e-05</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.3650251694210284</v>
+        <v>0.06581025827228758</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.599521431067185</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.730741142049904</v>
+        <v>0.1317450612097988</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.08429931533291091</v>
+        <v>-0.01519829364927153</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.280442246413334</v>
+        <v>0.05056083309596241</v>
       </c>
     </row>
     <row r="47">
@@ -38302,17 +38302,17 @@
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA47" t="n">
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.280442246413334</v>
+        <v>0.05056083309596241</v>
       </c>
     </row>
     <row r="48">
@@ -39097,17 +39097,17 @@
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA48" t="n">
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.280442246413334</v>
+        <v>0.05049346794002224</v>
       </c>
     </row>
     <row r="49">
@@ -39888,21 +39888,21 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0</v>
+        <v>0.2069603280649097</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA49" t="n">
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.2804279881757379</v>
+        <v>0.4648262304554276</v>
       </c>
     </row>
     <row r="50">
@@ -40683,21 +40683,21 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>-0.01330422598922544</v>
+        <v>0.03959946472118359</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA50" t="n">
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.2671237621865123</v>
+        <v>0.3367629381030302</v>
       </c>
     </row>
     <row r="51">
@@ -41478,21 +41478,21 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0</v>
+        <v>0.0693624355333953</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA51" t="n">
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.2671075471182023</v>
+        <v>0.4359076316691118</v>
       </c>
     </row>
     <row r="52">
@@ -42273,21 +42273,21 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.0003169759132606529</v>
+        <v>0.0379851555764479</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA52" t="n">
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.2695831116062182</v>
+        <v>0.4424561980214322</v>
       </c>
     </row>
     <row r="53">
@@ -43068,21 +43068,21 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0</v>
+        <v>0.01568861925315071</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA53" t="n">
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.265260529549235</v>
+        <v>0.4358079836439788</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.01535530292286688</v>
+        <v>0.0195461828627473</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.2981760116674632</v>
+        <v>0.4592153450370701</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.01048515662323026</v>
+        <v>0.01176817925537965</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.3037718213379378</v>
+        <v>0.463193604961955</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.009549229104648716</v>
+        <v>0.008945698889074837</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.3123790476400703</v>
+        <v>0.4693134159177437</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.00404588835762129</v>
+        <v>0.003953926535315225</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.3109127168518654</v>
+        <v>0.4682690490630101</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.003653408454284243</v>
+        <v>0.003137675919314173</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.3141741327922144</v>
+        <v>0.470587744349756</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.001807088051995362</v>
+        <v>0.001553422204039044</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.3141300235844797</v>
+        <v>0.4705549303812415</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.00107962559725581</v>
+        <v>0.0008997614318907874</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.314481029335424</v>
+        <v>0.470803118930717</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.0005373127986279048</v>
+        <v>0.0004488353163182084</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.3144752360842861</v>
+        <v>0.470797553875112</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.000261152010665445</v>
+        <v>0.0002192225566657728</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.314462269687641</v>
+        <v>0.4707868779063155</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0001547621399692484</v>
+        <v>0.0001251684583382067</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.314508033855255</v>
+        <v>0.4708178743160781</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>4.35752549678623e-05</v>
+        <v>3.740743216546624e-05</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.314442072416557</v>
+        <v>0.4707696475226011</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>2.038066370878316e-05</v>
+        <v>1.745791147271043e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.3144374203189872</v>
+        <v>0.470764896024337</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>9.09316673425382e-06</v>
+        <v>7.230980650542531e-06</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.314435207898448</v>
+        <v>0.4707618871525233</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>8.1188155095876e-07</v>
+        <v>-2.596391060734771e-07</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.3144296662257177</v>
+        <v>0.4707565006683657</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>-4.737170202826846e-08</v>
+        <v>-2.090799254370459e-06</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.3144268176530157</v>
+        <v>0.4707531160499149</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>-2.855390650193382e-06</v>
+        <v>-2.422504053549707e-06</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.314421150222742</v>
+        <v>0.4707474486196411</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.3144215307577998</v>
+        <v>0.4707478291546989</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.3144217590788345</v>
+        <v>0.4707480574757336</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.3144218490234844</v>
+        <v>0.4707481474203835</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.3144209910898996</v>
+        <v>0.4707472894867987</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.3144212194109343</v>
+        <v>0.4707475178078334</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.3144204237467225</v>
+        <v>0.4707467221436217</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.3144204860160956</v>
+        <v>0.4707467844129947</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.3144205136913725</v>
+        <v>0.4707468120882716</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.3144206659053957</v>
+        <v>0.4707469643022949</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.314420319964434</v>
+        <v>0.4707466183613331</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.3144203960714457</v>
+        <v>0.4707466944683448</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.3144205621231073</v>
+        <v>0.4707468605200064</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.3144209219017073</v>
+        <v>0.4707472202986064</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.314420942658165</v>
+        <v>0.4707472410550642</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.3144210464404535</v>
+        <v>0.4707473448373526</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.3144212747614882</v>
+        <v>0.4707475731583873</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.314421150222742</v>
+        <v>0.4707474486196411</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.3144211778980189</v>
+        <v>0.470747476294918</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.3144212332485728</v>
+        <v>0.470747531645472</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.3144214961637035</v>
+        <v>0.4707477945606026</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.3144214131378727</v>
+        <v>0.4707477115347719</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.3144212055732959</v>
+        <v>0.470747503970195</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.3144212194109343</v>
+        <v>0.4707475178078334</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.314421357787319</v>
+        <v>0.4707476561842181</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.3144210741157303</v>
+        <v>0.4707473725126295</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.3144209011452496</v>
+        <v>0.4707471995421487</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.3144207973629611</v>
+        <v>0.4707470957598602</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.314420942658165</v>
+        <v>0.4707472410550642</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.3144211848168382</v>
+        <v>0.4707474832137374</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.3144210118463572</v>
+        <v>0.4707473102432564</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.3144207143371303</v>
+        <v>0.4707470127340295</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.3144207004994918</v>
+        <v>0.4707469988963909</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.3144203338020726</v>
+        <v>0.4707466321989717</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.3144203338020726</v>
+        <v>0.4707466321989717</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.3144202715326995</v>
+        <v>0.4707465699295986</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.314420167750411</v>
+        <v>0.4707464661473101</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.3144199947799302</v>
+        <v>0.4707462931768294</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.3144200432116648</v>
+        <v>0.4707463416085639</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.3144196834330647</v>
+        <v>0.4707459818299639</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.3144196419201493</v>
+        <v>0.4707459403170485</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.314419697270703</v>
+        <v>0.4707459956676022</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.314419752621257</v>
+        <v>0.4707460510181561</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.3144197941341724</v>
+        <v>0.4707460925310715</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.3144195243002223</v>
+        <v>0.4707458226971214</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.3144195796507762</v>
+        <v>0.4707458780476754</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.3144197249459801</v>
+        <v>0.4707460233428792</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.3144196903518839</v>
+        <v>0.470745988748783</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.3144196765142453</v>
+        <v>0.4707459749111444</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.3144197664588955</v>
+        <v>0.4707460648557947</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.3144200847245802</v>
+        <v>0.4707463831214793</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.31441990483528</v>
+        <v>0.4707462032321791</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.3144199463481954</v>
+        <v>0.4707462447450946</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.3144197595400761</v>
+        <v>0.4707460579369753</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.3144198287282686</v>
+        <v>0.4707461271251678</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.3144196280825108</v>
+        <v>0.4707459264794099</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.3144196695954262</v>
+        <v>0.4707459679923253</v>
       </c>
     </row>
     <row r="126">
@@ -101103,7 +101103,7 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>-4.306599146602596e-06</v>
+        <v>-3.873712549958921e-06</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.314419697270703</v>
+        <v>0.4707459956676022</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-Mamba1_repeat_5_000006.xlsx
+++ b/out/LSTM-Mamba1_repeat_5_000006.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>1.599521431067185</v>
+        <v>1.262528981303212</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.599521431067185</v>
+        <v>1.262528981303212</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>2.199521431067184</v>
+        <v>1.462528981303212</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>2.199521431067184</v>
+        <v>1.462528981303212</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>2.199521431067184</v>
+        <v>1.462528981303212</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>2.199521431067184</v>
+        <v>1.462528981303212</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>2.199521431067184</v>
+        <v>1.462528981303212</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>2.199521431067184</v>
+        <v>1.462528981303212</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>2.199521431067184</v>
+        <v>1.462528981303212</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>1.599521431067185</v>
+        <v>1.262528981303212</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.599521431067185</v>
+        <v>1.262528981303212</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.599521431067185</v>
+        <v>1.262528981303212</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.599521431067185</v>
+        <v>1.262528981303212</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.599521431067185</v>
+        <v>1.262528981303212</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.599521431067185</v>
+        <v>1.262528981303212</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.599521431067185</v>
+        <v>1.262528981303212</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.599521431067185</v>
+        <v>1.262528981303212</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.599521431067185</v>
+        <v>1.262528981303212</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.599521431067185</v>
+        <v>1.262528981303212</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.599521431067185</v>
+        <v>1.262528981303212</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.599521431067185</v>
+        <v>1.262528981303212</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.599521431067185</v>
+        <v>1.262528981303212</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.599521431067185</v>
+        <v>1.262528981303212</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.599521431067185</v>
+        <v>1.262528981303212</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.599521431067185</v>
+        <v>1.262528981303212</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.599521431067185</v>
+        <v>1.262528981303212</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.599521431067185</v>
+        <v>1.262528981303212</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.599521431067185</v>
+        <v>1.262528981303212</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.599521431067185</v>
+        <v>1.262528981303212</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.599521431067185</v>
+        <v>1.262528981303212</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.599521431067185</v>
+        <v>1.262528981303212</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.599521431067185</v>
+        <v>1.262528981303212</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.599521431067185</v>
+        <v>1.262528981303212</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.599521431067185</v>
+        <v>1.262528981303212</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.599521431067185</v>
+        <v>1.262528981303212</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.599521431067185</v>
+        <v>1.262528981303212</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.599521431067185</v>
+        <v>1.262528981303212</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.599521431067185</v>
+        <v>1.262528981303212</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.599521431067185</v>
+        <v>1.262528981303212</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.599521431067185</v>
+        <v>1.262528981303212</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.599521431067185</v>
+        <v>1.262528981303212</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.599521431067185</v>
+        <v>1.262528981303212</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.599521431067185</v>
+        <v>1.262528981303212</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.000283607674783445</v>
+        <v>-0.0002449247141336091</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.3650251694210284</v>
+        <v>0.3152369753448964</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.599521431067185</v>
+        <v>0.5925037851595846</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.730741142049904</v>
+        <v>0.6310709525693897</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.08429931533291091</v>
+        <v>-0.07280127207385807</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.0775214109840431</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.280442246413334</v>
+        <v>0.2421907785569048</v>
       </c>
     </row>
     <row r="47">
@@ -38302,17 +38302,17 @@
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA47" t="n">
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.280442246413334</v>
+        <v>0.2421907785569048</v>
       </c>
     </row>
     <row r="48">
@@ -39097,17 +39097,17 @@
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA48" t="n">
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.280442246413334</v>
+        <v>0.2421448149398107</v>
       </c>
     </row>
     <row r="49">
@@ -39888,21 +39888,21 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0</v>
+        <v>0.1412101722337232</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA49" t="n">
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.2804279881757379</v>
+        <v>0.5248463418649354</v>
       </c>
     </row>
     <row r="50">
@@ -40683,21 +40683,21 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>-0.01330422598922544</v>
+        <v>0.02701891325286917</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA50" t="n">
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.2671237621865123</v>
+        <v>0.4374680518920019</v>
       </c>
     </row>
     <row r="51">
@@ -41478,21 +41478,21 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0</v>
+        <v>0.04732640652117693</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA51" t="n">
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.2671075471182023</v>
+        <v>0.5051150720123782</v>
       </c>
     </row>
     <row r="52">
@@ -42273,21 +42273,21 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.0003169759132606529</v>
+        <v>0.02591766244712186</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA52" t="n">
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.2695831116062182</v>
+        <v>0.5095831978825676</v>
       </c>
     </row>
     <row r="53">
@@ -43068,21 +43068,21 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0</v>
+        <v>0.0107032544009727</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA53" t="n">
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.265260529549235</v>
+        <v>0.5050461892704892</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.01535530292286688</v>
+        <v>0.01333592226564094</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.2981760116674632</v>
+        <v>0.5210168048187412</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.01048515662323026</v>
+        <v>0.008028505194432583</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.3037718213379378</v>
+        <v>0.5237296711413814</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.009549229104648716</v>
+        <v>0.006101669113602041</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.3123790476400703</v>
+        <v>0.5279035565710103</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.00404588835762129</v>
+        <v>0.002696796511455593</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.3109127168518654</v>
+        <v>0.527189375200771</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.003653408454284243</v>
+        <v>0.002138880041265688</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.3141741327922144</v>
+        <v>0.5287695605890006</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.001807088051995362</v>
+        <v>0.001058129111904645</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.3141300235844797</v>
+        <v>0.5287455863729194</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.00107962559725581</v>
+        <v>0.0006117505580734626</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.314481029335424</v>
+        <v>0.5289133078690991</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.0005373127986279048</v>
+        <v>0.0003033752790367313</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.3144752360842861</v>
+        <v>0.5289079239210596</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.000261152010665445</v>
+        <v>0.0001473563526062303</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.314462269687641</v>
+        <v>0.5288990325789349</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0001547621399692484</v>
+        <v>8.511662500337389e-05</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.314508033855255</v>
+        <v>0.5289189531703091</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>4.35752549678623e-05</v>
+        <v>2.40156114816348e-05</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.314442072416557</v>
+        <v>0.5288840273607478</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>2.038066370878316e-05</v>
+        <v>1.07205380308973e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.3144374203189872</v>
+        <v>0.5288792013119629</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>9.09316673425382e-06</v>
+        <v>2.338588390325519e-06</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.314435207898448</v>
+        <v>0.5288755966346322</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>8.1188155095876e-07</v>
+        <v>-2.596391060734771e-07</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.3144296662257177</v>
+        <v>0.5288702862574863</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>-4.737170202826846e-08</v>
+        <v>-2.090799254370459e-06</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.3144268176530157</v>
+        <v>0.5288663619711352</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>-2.855390650193382e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.314421150222742</v>
+        <v>0.5288660298678121</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.3144215307577998</v>
+        <v>0.5288664104028699</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.3144217590788345</v>
+        <v>0.5288666387239045</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.3144218490234844</v>
+        <v>0.5288667286685544</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.3144209910898996</v>
+        <v>0.5288658707349696</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.3144212194109343</v>
+        <v>0.5288660990560043</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.3144204237467225</v>
+        <v>0.5288653033917926</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.3144204860160956</v>
+        <v>0.5288653656611657</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.3144205136913725</v>
+        <v>0.5288653933364426</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.3144206659053957</v>
+        <v>0.5288655455504658</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.314420319964434</v>
+        <v>0.5288651996095041</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.3144203960714457</v>
+        <v>0.5288652757165158</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.3144205621231073</v>
+        <v>0.5288654417681773</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.3144209219017073</v>
+        <v>0.5288658015467773</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.314420942658165</v>
+        <v>0.5288658223032351</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.3144210464404535</v>
+        <v>0.5288659260855235</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.3144212747614882</v>
+        <v>0.5288661544065583</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.314421150222742</v>
+        <v>0.5288660298678121</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.3144211778980189</v>
+        <v>0.5288660575430889</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.3144212332485728</v>
+        <v>0.5288661128936428</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.3144214961637035</v>
+        <v>0.5288663758087736</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.3144214131378727</v>
+        <v>0.5288662927829427</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.3144212055732959</v>
+        <v>0.528866085218366</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.3144212194109343</v>
+        <v>0.5288660990560043</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.314421357787319</v>
+        <v>0.528866237432389</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.3144210741157303</v>
+        <v>0.5288659537608004</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.3144209011452496</v>
+        <v>0.5288657807903197</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.3144207973629611</v>
+        <v>0.5288656770080312</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.314420942658165</v>
+        <v>0.5288658223032351</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.3144211848168382</v>
+        <v>0.5288660644619083</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.3144210118463572</v>
+        <v>0.5288658914914273</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.3144207143371303</v>
+        <v>0.5288655939822003</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.3144207004994918</v>
+        <v>0.5288655801445619</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.3144203338020726</v>
+        <v>0.5288652134471427</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.3144203338020726</v>
+        <v>0.5288652134471427</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.3144202715326995</v>
+        <v>0.5288651511777696</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.314420167750411</v>
+        <v>0.528865047395481</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.3144199947799302</v>
+        <v>0.5288648744250003</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.3144200432116648</v>
+        <v>0.5288649228567348</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.3144196834330647</v>
+        <v>0.5288645630781348</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.3144196419201493</v>
+        <v>0.5288645215652193</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.314419697270703</v>
+        <v>0.528864576915773</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.314419752621257</v>
+        <v>0.5288646322663271</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.3144197941341724</v>
+        <v>0.5288646737792424</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.3144195243002223</v>
+        <v>0.5288644039452923</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.3144195796507762</v>
+        <v>0.5288644592958462</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.3144197249459801</v>
+        <v>0.5288646045910502</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.3144196903518839</v>
+        <v>0.528864569996954</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.3144196765142453</v>
+        <v>0.5288645561593154</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.3144197664588955</v>
+        <v>0.5288646461039656</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.3144200847245802</v>
+        <v>0.5288649643696502</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.31441990483528</v>
+        <v>0.5288647844803501</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.3144199463481954</v>
+        <v>0.5288648259932655</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.3144197595400761</v>
+        <v>0.5288646391851461</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.3144198287282686</v>
+        <v>0.5288647083733387</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.3144196280825108</v>
+        <v>0.5288645077275809</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.3144196695954262</v>
+        <v>0.5288645492404962</v>
       </c>
     </row>
     <row r="126">
@@ -101103,7 +101103,7 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>-4.306599146602596e-06</v>
+        <v>-3.873712549958921e-06</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.314419697270703</v>
+        <v>0.528864576915773</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-Mamba1_repeat_5_000006.xlsx
+++ b/out/LSTM-Mamba1_repeat_5_000006.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>1</v>
+        <v>0.01727910339832306</v>
       </c>
       <c r="JB2" t="n">
-        <v>1.262528981303212</v>
+        <v>-0.3</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.009741038084030151</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.262528981303212</v>
+        <v>-0.3</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.005708342418074608</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.462528981303212</v>
+        <v>-0.3</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.00366254523396492</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.462528981303212</v>
+        <v>-0.3</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0.002462774515151978</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.462528981303212</v>
+        <v>-0.3</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0.001889484003186226</v>
       </c>
       <c r="JB7" t="n">
-        <v>1.462528981303212</v>
+        <v>-0.3</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0.00149044580757618</v>
       </c>
       <c r="JB8" t="n">
-        <v>1.462528981303212</v>
+        <v>-0.3</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0.001401510089635849</v>
       </c>
       <c r="JB9" t="n">
-        <v>1.462528981303212</v>
+        <v>-0.3</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0.00139334425330162</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.462528981303212</v>
+        <v>-0.3</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0.001280462369322777</v>
       </c>
       <c r="JB11" t="n">
-        <v>1.262528981303212</v>
+        <v>-0.3</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0.001188384369015694</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.262528981303212</v>
+        <v>-0.3</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0.001120617613196373</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.262528981303212</v>
+        <v>-0.3</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.001230910420417786</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.262528981303212</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.001211462542414665</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.262528981303212</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.001160973682999611</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.262528981303212</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.001133674755692482</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.262528981303212</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.001219548285007477</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.262528981303212</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.001338604837656021</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.262528981303212</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.00148901529610157</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.262528981303212</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.001417063176631927</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.262528981303212</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.001270238310098648</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.262528981303212</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.001136576756834984</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.262528981303212</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0.001097159460186958</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.262528981303212</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.001260591670870781</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.262528981303212</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.001226922497153282</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.262528981303212</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.001415513455867767</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.262528981303212</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.001757888123393059</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.262528981303212</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.001580903306603432</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.262528981303212</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.001183213666081429</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.262528981303212</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.0009345952421426773</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.262528981303212</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.000685669481754303</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.262528981303212</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0.0005067605525255203</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.262528981303212</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.000500822439789772</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.262528981303212</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.0007930342108011246</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.262528981303212</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.0008027013391256332</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.262528981303212</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.0007100924849510193</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.262528981303212</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.0007079336792230606</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.262528981303212</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.000550098717212677</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.262528981303212</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.0004650354385375977</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.262528981303212</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.0004845857620239258</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.262528981303212</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.0006583165377378464</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.262528981303212</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,14 +35122,14 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.000813586637377739</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.262528981303212</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.0009717531502246857</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.262528981303212</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0002449247141336091</v>
+        <v>-7.015488043695223e-05</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.3152369753448964</v>
+        <v>0.09029458546233551</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.0005816705524921417</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.5925037851595846</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.6310709525693897</v>
+        <v>0.1807604735990374</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.07280127207385807</v>
+        <v>-0.02085282839112443</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>-0.0003320276737213135</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.0775214109840431</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.2421907785569048</v>
+        <v>0.06937160219077416</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-0.0007092375308275223</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.2421907785569048</v>
+        <v>0.06937160219077416</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.0008378680795431137</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.2421448149398107</v>
+        <v>0.06935478411541716</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.1412101722337232</v>
+        <v>0.05166876473087183</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.001151205971837044</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.5248463418649354</v>
+        <v>0.1727951981641732</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.02701891325286917</v>
+        <v>0.009886173848765348</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-0.001042304560542107</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.4374680518920019</v>
+        <v>0.1408235050465753</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.04732640652117693</v>
+        <v>0.01731678861861667</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.001146925613284111</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.5051150720123782</v>
+        <v>0.1655756304288327</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.02591766244712186</v>
+        <v>0.009481784510021157</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.001352118328213692</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.5095831978825676</v>
+        <v>0.1672090039105665</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0107032544009727</v>
+        <v>0.003913038217609705</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.001610932871699333</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.5050461892704892</v>
+        <v>0.1655457367417936</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.01333592226564094</v>
+        <v>0.004876303836990783</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.001488419249653816</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.5210168048187412</v>
+        <v>0.1713864201975269</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.008028505194432583</v>
+        <v>0.0029347500990952</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.0019697155803442</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.5237296711413814</v>
+        <v>0.1723759857822787</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.006101669113602041</v>
+        <v>0.002229979810921135</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>-0.002226008102297783</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.5279035565710103</v>
+        <v>0.1739001906809159</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.002696796511455593</v>
+        <v>0.0009835396647796346</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.003223007544875145</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.527189375200771</v>
+        <v>0.1736357137325108</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.002138880041265688</v>
+        <v>0.0007794078739219165</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>-0.004057945683598518</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.5287695605890006</v>
+        <v>0.174210705092204</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.001058129111904645</v>
+        <v>0.0003827294408122823</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>-0.003815853968262672</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.5287455863729194</v>
+        <v>0.1741987643275284</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.0006117505580734626</v>
+        <v>0.0002219176581591042</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.004129102453589439</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.5289133078690991</v>
+        <v>0.1742571626119432</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.0003033752790367313</v>
+        <v>0.0001084588290795521</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.005412017926573753</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.5289079239210596</v>
+        <v>0.1742520213480419</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0001473563526062303</v>
+        <v>4.961831508525235e-05</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.006327277049422264</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.5288990325789349</v>
+        <v>0.1742456041461618</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>8.511662500337389e-05</v>
+        <v>2.837652777902737e-05</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.00706133060157299</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.5289189531703091</v>
+        <v>0.1742498339948189</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>2.40156114816348e-05</v>
+        <v>6.159850569859539e-06</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.007602067664265633</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.5288840273607478</v>
+        <v>0.174233749841556</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>1.07205380308973e-05</v>
+        <v>-5.08417705457914e-07</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>-0.007658777758479118</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.5288792013119629</v>
+        <v>0.1742288133795415</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>2.338588390325519e-06</v>
+        <v>-2.553803869891494e-06</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>-0.007599612697958946</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.5288755966346322</v>
+        <v>0.1742244122509365</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>-2.596391060734771e-07</v>
+        <v>-2.629819553036738e-06</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>-0.007126452401280403</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.5288702862574863</v>
+        <v>0.1742192570623637</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>-2.090799254370459e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.00690883956849575</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.5288663619711352</v>
+        <v>0.1742197967302639</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.006774963811039925</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.5288660298678121</v>
+        <v>0.1742194646269407</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.006654249504208565</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.5288664104028699</v>
+        <v>0.1742198451619984</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.00697946734726429</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.5288666387239045</v>
+        <v>0.1742200734830331</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.007328132167458534</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.5288667286685544</v>
+        <v>0.1742201634276831</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.007368003949522972</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.5288658707349696</v>
+        <v>0.1742193054940982</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.007267290726304054</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.5288660990560043</v>
+        <v>0.1742195338151329</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.006919803097844124</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.5288653033917926</v>
+        <v>0.1742187381509212</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.006723271682858467</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.5288653656611657</v>
+        <v>0.1742188004202943</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.006394127383828163</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.5288653933364426</v>
+        <v>0.1742188280955711</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.006003277376294136</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.5288655455504658</v>
+        <v>0.1742189803095944</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.005868175998330116</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.5288651996095041</v>
+        <v>0.1742186343686327</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.005625048652291298</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.7475466071276708</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.5288652757165158</v>
+        <v>0.1742187104756443</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.005540410056710243</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.7475466071276708</v>
+        <v>0.3</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.5288654417681773</v>
+        <v>0.1742188765273059</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.005210919305682182</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.7475466071276708</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.5288658015467773</v>
+        <v>0.174219236305906</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.005114251747727394</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.7475466071276708</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.5288658223032351</v>
+        <v>0.1742192570623637</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.005127778276801109</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.7475466071276708</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.5288659260855235</v>
+        <v>0.1742193608446522</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.00560111366212368</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.7475466071276708</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.5288661544065583</v>
+        <v>0.1742195891656869</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.006051672622561455</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.7475466071276708</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.5288660298678121</v>
+        <v>0.1742194646269407</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-0.00629868172109127</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.7475466071276708</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.5288660575430889</v>
+        <v>0.1742194923022175</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>-0.00614125095307827</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.3</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.5288661128936428</v>
+        <v>0.1742195476527715</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.006317527964711189</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.3</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.5288663758087736</v>
+        <v>0.1742198105679022</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.006438190117478371</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.3</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.5288662927829427</v>
+        <v>0.1742197275420714</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.006464803591370583</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.3</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.528866085218366</v>
+        <v>0.1742195199774946</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.006424201652407646</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.3</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.5288660990560043</v>
+        <v>0.1742195338151329</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.006424816325306892</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.3</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.528866237432389</v>
+        <v>0.1742196721915177</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.006442708894610405</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.16</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.5288659537608004</v>
+        <v>0.174219388519929</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.006363941356539726</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.7475466071276708</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.5288657807903197</v>
+        <v>0.1742192155494483</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.005994467064738274</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.7475466071276708</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.5288656770080312</v>
+        <v>0.1742191117671598</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.005762448534369469</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.7475466071276708</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.5288658223032351</v>
+        <v>0.1742192570623637</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.005737127736210823</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.7475466071276708</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.5288660644619083</v>
+        <v>0.1742194992210369</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.00584816001355648</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.7475466071276708</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.5288658914914273</v>
+        <v>0.1742193262505559</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.005829343572258949</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.7475466071276708</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.5288655939822003</v>
+        <v>0.174219028741329</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.005757516250014305</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.7475466071276708</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.5288655801445619</v>
+        <v>0.1742190149036904</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.005566706880927086</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.7475466071276708</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.5288652134471427</v>
+        <v>0.1742186482062712</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.005221685394644737</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.7475466071276708</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.5288652134471427</v>
+        <v>0.1742186482062712</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.004994610324501991</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.7475466071276708</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.5288651511777696</v>
+        <v>0.1742185859368981</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.004960143938660622</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.7475466071276708</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.528865047395481</v>
+        <v>0.1742184821546096</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.00483064167201519</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.7475466071276708</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.5288648744250003</v>
+        <v>0.1742183091841289</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.004673795774579048</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.7475466071276708</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.5288649228567348</v>
+        <v>0.1742183576158634</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.004489010199904442</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.7475466071276708</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.5288645630781348</v>
+        <v>0.1742179978372634</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.004220498725771904</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.7475466071276708</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.5288645215652193</v>
+        <v>0.174217956324348</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.003891462460160255</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.7475466071276708</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.528864576915773</v>
+        <v>0.1742180116749017</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.003762172535061836</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.7475466071276708</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.5288646322663271</v>
+        <v>0.1742180670254556</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.003686653450131416</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.7475466071276708</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.5288646737792424</v>
+        <v>0.1742181085383711</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.003581168130040169</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.7475466071276708</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.5288644039452923</v>
+        <v>0.174217838704421</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-0.003392228856682777</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.7475466071276708</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.5288644592958462</v>
+        <v>0.1742178940549749</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.003315979614853859</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.7475466071276708</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.5288646045910502</v>
+        <v>0.1742180393501788</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-0.003251319751143456</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.7475466071276708</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.528864569996954</v>
+        <v>0.1742180047560825</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.003257127478718758</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.7475466071276708</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.5288645561593154</v>
+        <v>0.174217990918444</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.002996461465954781</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.7475466071276708</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.5288646461039656</v>
+        <v>0.1742180808630942</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.002781478688120842</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.7475466071276708</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.5288649643696502</v>
+        <v>0.1742183991287788</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.003234507516026497</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.7475466071276708</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.5288647844803501</v>
+        <v>0.1742182192394787</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.003669245168566704</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.5288648259932655</v>
+        <v>0.1742182607523941</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.003851370885968208</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.16</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.5288646391851461</v>
+        <v>0.1742180739442748</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.003996303305029869</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.3</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.5288647083733387</v>
+        <v>0.1742181431324673</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.003921320661902428</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.16</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.5288645077275809</v>
+        <v>0.1742179424867094</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.003814836964011192</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.01999999999999985</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.5288645492404962</v>
+        <v>0.1742179839996248</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.003630710765719414</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.7475466071276708</v>
+        <v>0.1200000000000001</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.528864576915773</v>
+        <v>0.1742180116749017</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-Mamba1_repeat_5_000006.xlsx
+++ b/out/LSTM-Mamba1_repeat_5_000006.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0.01727910339832306</v>
+        <v>0.01727909222245216</v>
       </c>
       <c r="JB2" t="n">
         <v>-0.3</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0.009741038084030151</v>
+        <v>0.009741079062223434</v>
       </c>
       <c r="JB3" t="n">
         <v>-0.3</v>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0.005708342418074608</v>
+        <v>0.005708400160074234</v>
       </c>
       <c r="JB4" t="n">
         <v>-0.3</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0.00366254523396492</v>
+        <v>0.003662580624222755</v>
       </c>
       <c r="JB5" t="n">
         <v>-0.3</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0.002462774515151978</v>
+        <v>0.002462778240442276</v>
       </c>
       <c r="JB6" t="n">
         <v>-0.3</v>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0.001889484003186226</v>
+        <v>0.001889446750283241</v>
       </c>
       <c r="JB7" t="n">
         <v>-0.3</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0.00149044580757618</v>
+        <v>0.001490449532866478</v>
       </c>
       <c r="JB8" t="n">
         <v>-0.3</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0.001401510089635849</v>
+        <v>0.001401541754603386</v>
       </c>
       <c r="JB9" t="n">
         <v>-0.3</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0.001280462369322777</v>
+        <v>0.001280469819903374</v>
       </c>
       <c r="JB11" t="n">
         <v>-0.3</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0.001188384369015694</v>
+        <v>0.001188389956951141</v>
       </c>
       <c r="JB12" t="n">
         <v>-0.3</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0.001120617613196373</v>
+        <v>0.001120572909712791</v>
       </c>
       <c r="JB13" t="n">
         <v>-0.3</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0.001230910420417786</v>
+        <v>0.001230936497449875</v>
       </c>
       <c r="JB14" t="n">
         <v>-0.4399999999999999</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0.001211462542414665</v>
+        <v>0.001211510971188545</v>
       </c>
       <c r="JB15" t="n">
         <v>-0.5799999999999998</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0.001160973682999611</v>
+        <v>0.001160977408289909</v>
       </c>
       <c r="JB16" t="n">
         <v>-0.7199999999999999</v>
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0.001133674755692482</v>
+        <v>0.001133684068918228</v>
       </c>
       <c r="JB17" t="n">
         <v>-0.8599999999999999</v>
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0.001219548285007477</v>
+        <v>0.001219535246491432</v>
       </c>
       <c r="JB18" t="n">
         <v>-0.9999999999999998</v>
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0.001338604837656021</v>
+        <v>0.001338651403784752</v>
       </c>
       <c r="JB19" t="n">
         <v>-0.9999999999999998</v>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0.00148901529610157</v>
+        <v>0.001489056274294853</v>
       </c>
       <c r="JB20" t="n">
         <v>-0.9999999999999998</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0.001417063176631927</v>
+        <v>0.001417098566889763</v>
       </c>
       <c r="JB21" t="n">
         <v>-0.9999999999999998</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0.001270238310098648</v>
+        <v>0.001270279288291931</v>
       </c>
       <c r="JB22" t="n">
         <v>-0.9999999999999998</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0.001136576756834984</v>
+        <v>0.001136587932705879</v>
       </c>
       <c r="JB23" t="n">
         <v>-0.9999999999999998</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0.001097159460186958</v>
+        <v>0.001097187399864197</v>
       </c>
       <c r="JB24" t="n">
         <v>-0.9999999999999998</v>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0.001260591670870781</v>
+        <v>0.001260599121451378</v>
       </c>
       <c r="JB25" t="n">
         <v>-0.9999999999999998</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0.001226922497153282</v>
+        <v>0.001226888969540596</v>
       </c>
       <c r="JB26" t="n">
         <v>-0.9999999999999998</v>
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0.001415513455867767</v>
+        <v>0.001415461301803589</v>
       </c>
       <c r="JB27" t="n">
         <v>-0.9999999999999998</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0.001757888123393059</v>
+        <v>0.001757849007844925</v>
       </c>
       <c r="JB28" t="n">
         <v>-0.9999999999999998</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0.001580903306603432</v>
+        <v>0.001580862328410149</v>
       </c>
       <c r="JB29" t="n">
         <v>-0.9999999999999998</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0.001183213666081429</v>
+        <v>0.001183198764920235</v>
       </c>
       <c r="JB30" t="n">
         <v>-0.9999999999999998</v>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0.0009345952421426773</v>
+        <v>0.0009345579892396927</v>
       </c>
       <c r="JB31" t="n">
         <v>-0.9999999999999998</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0.000685669481754303</v>
+        <v>0.0006856434047222137</v>
       </c>
       <c r="JB32" t="n">
         <v>-0.9999999999999998</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0.0005067605525255203</v>
+        <v>0.0005067288875579834</v>
       </c>
       <c r="JB33" t="n">
         <v>-0.9999999999999998</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0.000500822439789772</v>
+        <v>0.0005008615553379059</v>
       </c>
       <c r="JB34" t="n">
         <v>-0.9999999999999998</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0.0007930342108011246</v>
+        <v>0.0007930230349302292</v>
       </c>
       <c r="JB35" t="n">
         <v>-0.9999999999999998</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0.0008027013391256332</v>
+        <v>0.000802699476480484</v>
       </c>
       <c r="JB36" t="n">
         <v>-0.9999999999999998</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0.0007100924849510193</v>
+        <v>0.0007100943475961685</v>
       </c>
       <c r="JB37" t="n">
         <v>-0.9999999999999998</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0.0007079336792230606</v>
+        <v>0.0007079374045133591</v>
       </c>
       <c r="JB38" t="n">
         <v>-0.9999999999999998</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0.000550098717212677</v>
+        <v>0.0005500763654708862</v>
       </c>
       <c r="JB39" t="n">
         <v>-0.9999999999999998</v>
@@ -33536,7 +33536,7 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0.0004845857620239258</v>
+        <v>0.000484563410282135</v>
       </c>
       <c r="JB41" t="n">
         <v>-0.9999999999999998</v>
@@ -34331,7 +34331,7 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0.0006583165377378464</v>
+        <v>0.0006582494825124741</v>
       </c>
       <c r="JB42" t="n">
         <v>-0.2599999999999998</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0.000813586637377739</v>
+        <v>0.0008135214447975159</v>
       </c>
       <c r="JB43" t="n">
         <v>-0.2599999999999998</v>
@@ -35921,7 +35921,7 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0.0009717531502246857</v>
+        <v>0.0009716954082250595</v>
       </c>
       <c r="JB44" t="n">
         <v>-0.2599999999999998</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0.0005816705524921417</v>
+        <v>0.0005816053599119186</v>
       </c>
       <c r="JB45" t="n">
         <v>-0.2599999999999998</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>-0.0003320276737213135</v>
+        <v>-0.0003321021795272827</v>
       </c>
       <c r="JB46" t="n">
         <v>-0.2599999999999998</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>-0.0007092375308275223</v>
+        <v>-0.0007092691957950592</v>
       </c>
       <c r="JB47" t="n">
         <v>-0.3999999999999999</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>-0.0008378680795431137</v>
+        <v>-0.000838015228509903</v>
       </c>
       <c r="JB48" t="n">
         <v>-0.9999999999999998</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>-0.001151205971837044</v>
+        <v>-0.001151304692029953</v>
       </c>
       <c r="JB49" t="n">
         <v>-0.9999999999999998</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>-0.001042304560542107</v>
+        <v>-0.001042395830154419</v>
       </c>
       <c r="JB50" t="n">
         <v>-0.9999999999999998</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>-0.001146925613284111</v>
+        <v>-0.001147080212831497</v>
       </c>
       <c r="JB51" t="n">
         <v>-0.9999999999999998</v>
@@ -42281,7 +42281,7 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>-0.001352118328213692</v>
+        <v>-0.001352217048406601</v>
       </c>
       <c r="JB52" t="n">
         <v>-0.9999999999999998</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>-0.001610932871699333</v>
+        <v>-0.001610968261957169</v>
       </c>
       <c r="JB53" t="n">
         <v>-0.9999999999999998</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>-0.001488419249653816</v>
+        <v>-0.001488525420427322</v>
       </c>
       <c r="JB54" t="n">
         <v>-0.9999999999999998</v>
@@ -44666,7 +44666,7 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>-0.0019697155803442</v>
+        <v>-0.001969832926988602</v>
       </c>
       <c r="JB55" t="n">
         <v>-0.9999999999999998</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>-0.002226008102297783</v>
+        <v>-0.002226009964942932</v>
       </c>
       <c r="JB56" t="n">
         <v>-0.9999999999999998</v>
@@ -46256,7 +46256,7 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>-0.003223007544875145</v>
+        <v>-0.00322302058339119</v>
       </c>
       <c r="JB57" t="n">
         <v>-0.9999999999999998</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>-0.004057945683598518</v>
+        <v>-0.004057921469211578</v>
       </c>
       <c r="JB58" t="n">
         <v>-0.9999999999999998</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>-0.003815853968262672</v>
+        <v>-0.003815785050392151</v>
       </c>
       <c r="JB59" t="n">
         <v>-0.9999999999999998</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>-0.004129102453589439</v>
+        <v>-0.004129040986299515</v>
       </c>
       <c r="JB60" t="n">
         <v>-0.9999999999999998</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>-0.005412017926573753</v>
+        <v>-0.005412057042121887</v>
       </c>
       <c r="JB61" t="n">
         <v>-0.9999999999999998</v>
@@ -50231,7 +50231,7 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>-0.006327277049422264</v>
+        <v>-0.00632718950510025</v>
       </c>
       <c r="JB62" t="n">
         <v>-0.9999999999999998</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>-0.00706133060157299</v>
+        <v>-0.007061250507831573</v>
       </c>
       <c r="JB63" t="n">
         <v>-0.9999999999999998</v>
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>-0.007602067664265633</v>
+        <v>-0.007602021098136902</v>
       </c>
       <c r="JB64" t="n">
         <v>-0.9999999999999998</v>
@@ -52616,7 +52616,7 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>-0.007658777758479118</v>
+        <v>-0.007658772170543671</v>
       </c>
       <c r="JB65" t="n">
         <v>-0.9999999999999998</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>-0.007599612697958946</v>
+        <v>-0.007599625736474991</v>
       </c>
       <c r="JB66" t="n">
         <v>-0.9999999999999998</v>
@@ -54206,7 +54206,7 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>-0.007126452401280403</v>
+        <v>-0.007126588374376297</v>
       </c>
       <c r="JB67" t="n">
         <v>-0.9999999999999998</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>-0.00690883956849575</v>
+        <v>-0.006908945739269257</v>
       </c>
       <c r="JB68" t="n">
         <v>-0.9999999999999998</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>-0.006774963811039925</v>
+        <v>-0.006775137037038803</v>
       </c>
       <c r="JB69" t="n">
         <v>-0.9999999999999998</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>-0.006654249504208565</v>
+        <v>-0.006654448807239532</v>
       </c>
       <c r="JB70" t="n">
         <v>-0.9999999999999998</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>-0.00697946734726429</v>
+        <v>-0.006979599595069885</v>
       </c>
       <c r="JB71" t="n">
         <v>-0.9999999999999998</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>-0.007328132167458534</v>
+        <v>-0.007328290492296219</v>
       </c>
       <c r="JB72" t="n">
         <v>-0.9999999999999998</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>-0.007368003949522972</v>
+        <v>-0.007368132472038269</v>
       </c>
       <c r="JB73" t="n">
         <v>-0.9999999999999998</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>-0.007267290726304054</v>
+        <v>-0.007267516106367111</v>
       </c>
       <c r="JB74" t="n">
         <v>-0.9999999999999998</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>-0.006919803097844124</v>
+        <v>-0.006919894367456436</v>
       </c>
       <c r="JB75" t="n">
         <v>-0.9999999999999998</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>-0.006723271682858467</v>
+        <v>-0.006723348051309586</v>
       </c>
       <c r="JB76" t="n">
         <v>-0.9999999999999998</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>-0.006394127383828163</v>
+        <v>-0.006394237279891968</v>
       </c>
       <c r="JB77" t="n">
         <v>-0.9999999999999998</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>-0.006003277376294136</v>
+        <v>-0.006003335118293762</v>
       </c>
       <c r="JB78" t="n">
         <v>-0.9999999999999998</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>-0.005868175998330116</v>
+        <v>-0.005868230015039444</v>
       </c>
       <c r="JB79" t="n">
         <v>-0.2599999999999998</v>
@@ -64541,7 +64541,7 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>-0.005625048652291298</v>
+        <v>-0.005625158548355103</v>
       </c>
       <c r="JB80" t="n">
         <v>0.02000000000000007</v>
@@ -65336,7 +65336,7 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>-0.005540410056710243</v>
+        <v>-0.005540464073419571</v>
       </c>
       <c r="JB81" t="n">
         <v>0.3</v>
@@ -66131,7 +66131,7 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>-0.005210919305682182</v>
+        <v>-0.005210991948843002</v>
       </c>
       <c r="JB82" t="n">
         <v>0.5799999999999998</v>
@@ -66926,7 +66926,7 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>-0.005114251747727394</v>
+        <v>-0.005114302039146423</v>
       </c>
       <c r="JB83" t="n">
         <v>0.8599999999999999</v>
@@ -67721,7 +67721,7 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>-0.005127778276801109</v>
+        <v>-0.005127858370542526</v>
       </c>
       <c r="JB84" t="n">
         <v>0.8599999999999999</v>
@@ -68516,7 +68516,7 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>-0.00560111366212368</v>
+        <v>-0.005601253360509872</v>
       </c>
       <c r="JB85" t="n">
         <v>0.7199999999999999</v>
@@ -69311,7 +69311,7 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>-0.006051672622561455</v>
+        <v>-0.006051767617464066</v>
       </c>
       <c r="JB86" t="n">
         <v>0.5799999999999998</v>
@@ -70106,7 +70106,7 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>-0.00629868172109127</v>
+        <v>-0.00629865750670433</v>
       </c>
       <c r="JB87" t="n">
         <v>0.4399999999999999</v>
@@ -70901,7 +70901,7 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>-0.00614125095307827</v>
+        <v>-0.006141308695077896</v>
       </c>
       <c r="JB88" t="n">
         <v>-0.3</v>
@@ -71696,7 +71696,7 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>-0.006317527964711189</v>
+        <v>-0.006317511200904846</v>
       </c>
       <c r="JB89" t="n">
         <v>-0.3</v>
@@ -72491,7 +72491,7 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>-0.006438190117478371</v>
+        <v>-0.006438136100769043</v>
       </c>
       <c r="JB90" t="n">
         <v>-0.3</v>
@@ -73286,7 +73286,7 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>-0.006464803591370583</v>
+        <v>-0.006464820355176926</v>
       </c>
       <c r="JB91" t="n">
         <v>-0.3</v>
@@ -74081,7 +74081,7 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>-0.006424201652407646</v>
+        <v>-0.00642428919672966</v>
       </c>
       <c r="JB92" t="n">
         <v>-0.3</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>-0.006424816325306892</v>
+        <v>-0.006424926221370697</v>
       </c>
       <c r="JB93" t="n">
         <v>-0.3</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>-0.006442708894610405</v>
+        <v>-0.00644272193312645</v>
       </c>
       <c r="JB94" t="n">
         <v>-0.16</v>
@@ -76466,7 +76466,7 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>-0.006363941356539726</v>
+        <v>-0.006363991647958755</v>
       </c>
       <c r="JB95" t="n">
         <v>0.5799999999999998</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>-0.005994467064738274</v>
+        <v>-0.005994487553834915</v>
       </c>
       <c r="JB96" t="n">
         <v>0.7199999999999999</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>-0.005762448534369469</v>
+        <v>-0.00576261430978775</v>
       </c>
       <c r="JB97" t="n">
         <v>0.8599999999999999</v>
@@ -78851,7 +78851,7 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>-0.005737127736210823</v>
+        <v>-0.00573701411485672</v>
       </c>
       <c r="JB98" t="n">
         <v>0.9999999999999998</v>
@@ -79646,7 +79646,7 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>-0.00584816001355648</v>
+        <v>-0.005848105996847153</v>
       </c>
       <c r="JB99" t="n">
         <v>0.9999999999999998</v>
@@ -80441,7 +80441,7 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>-0.005829343572258949</v>
+        <v>-0.005829386413097382</v>
       </c>
       <c r="JB100" t="n">
         <v>0.9999999999999998</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>-0.005757516250014305</v>
+        <v>-0.005757506936788559</v>
       </c>
       <c r="JB101" t="n">
         <v>0.9999999999999998</v>
@@ -82031,7 +82031,7 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>-0.005566706880927086</v>
+        <v>-0.005566708743572235</v>
       </c>
       <c r="JB102" t="n">
         <v>0.9999999999999998</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>-0.005221685394644737</v>
+        <v>-0.005221832543611526</v>
       </c>
       <c r="JB103" t="n">
         <v>0.9999999999999998</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>-0.004994610324501991</v>
+        <v>-0.004994791001081467</v>
       </c>
       <c r="JB104" t="n">
         <v>0.9999999999999998</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>-0.004960143938660622</v>
+        <v>-0.004960261285305023</v>
       </c>
       <c r="JB105" t="n">
         <v>0.9999999999999998</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>-0.00483064167201519</v>
+        <v>-0.004830572754144669</v>
       </c>
       <c r="JB106" t="n">
         <v>0.9999999999999998</v>
@@ -86006,7 +86006,7 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>-0.004673795774579048</v>
+        <v>-0.004673704504966736</v>
       </c>
       <c r="JB107" t="n">
         <v>0.3999999999999999</v>
@@ -86801,7 +86801,7 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>-0.004489010199904442</v>
+        <v>-0.004488900303840637</v>
       </c>
       <c r="JB108" t="n">
         <v>0.3999999999999999</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>-0.004220498725771904</v>
+        <v>-0.004220485687255859</v>
       </c>
       <c r="JB109" t="n">
         <v>0.3999999999999999</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>-0.003891462460160255</v>
+        <v>-0.003891516476869583</v>
       </c>
       <c r="JB110" t="n">
         <v>0.3999999999999999</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>-0.003762172535061836</v>
+        <v>-0.003762166947126389</v>
       </c>
       <c r="JB111" t="n">
         <v>0.3999999999999999</v>
@@ -89981,7 +89981,7 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>-0.003686653450131416</v>
+        <v>-0.003686647862195969</v>
       </c>
       <c r="JB112" t="n">
         <v>0.3999999999999999</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>-0.003581168130040169</v>
+        <v>-0.003581184893846512</v>
       </c>
       <c r="JB113" t="n">
         <v>0.3999999999999999</v>
@@ -91571,7 +91571,7 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>-0.003392228856682777</v>
+        <v>-0.003392219543457031</v>
       </c>
       <c r="JB114" t="n">
         <v>0.3999999999999999</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>-0.003315979614853859</v>
+        <v>-0.003315974026918411</v>
       </c>
       <c r="JB115" t="n">
         <v>0.3999999999999999</v>
@@ -93161,7 +93161,7 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>-0.003251319751143456</v>
+        <v>-0.003251250833272934</v>
       </c>
       <c r="JB116" t="n">
         <v>0.3999999999999999</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>-0.003257127478718758</v>
+        <v>-0.003257092088460922</v>
       </c>
       <c r="JB117" t="n">
         <v>0.3999999999999999</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>-0.002996461465954781</v>
+        <v>-0.002996467053890228</v>
       </c>
       <c r="JB118" t="n">
         <v>0.3999999999999999</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>-0.002781478688120842</v>
+        <v>-0.002781514078378677</v>
       </c>
       <c r="JB119" t="n">
         <v>0.2599999999999998</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>-0.003234507516026497</v>
+        <v>-0.0032346211373806</v>
       </c>
       <c r="JB120" t="n">
         <v>0.1199999999999999</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>-0.003669245168566704</v>
+        <v>-0.003669284284114838</v>
       </c>
       <c r="JB121" t="n">
         <v>-0.02000000000000007</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>-0.003851370885968208</v>
+        <v>-0.003851380199193954</v>
       </c>
       <c r="JB122" t="n">
         <v>-0.16</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>-0.003996303305029869</v>
+        <v>-0.003996327519416809</v>
       </c>
       <c r="JB123" t="n">
         <v>-0.3</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>-0.003921320661902428</v>
+        <v>-0.003921397030353546</v>
       </c>
       <c r="JB124" t="n">
         <v>-0.16</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>-0.003814836964011192</v>
+        <v>-0.003814846277236938</v>
       </c>
       <c r="JB125" t="n">
         <v>-0.01999999999999985</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>-0.003630710765719414</v>
+        <v>-0.003630723804235458</v>
       </c>
       <c r="JB126" t="n">
         <v>0.1200000000000001</v>
